--- a/output/graficos_dimensiones/comunal_p_aps_a_2020_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_p_aps_a_2020_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 23:37</t>
+    <t xml:space="preserve">2026-08-17 14:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_aps_a_2020_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_p_aps_a_2020_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-17 14:41</t>
+    <t xml:space="preserve">2026-08-17 20:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_aps_a_2020_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_p_aps_a_2020_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-17 20:42</t>
+    <t xml:space="preserve">2026-09-06 20:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
